--- a/crdo/dist/20261025_Credo模型_v0.2.xlsx
+++ b/crdo/dist/20261025_Credo模型_v0.2.xlsx
@@ -5604,7 +5604,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5841,7 +5841,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5962,7 +5962,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6083,7 +6083,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6204,7 +6204,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6325,7 +6325,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
